--- a/scripts/teacher-imports/assignments/inputs/المعلمات.xlsx
+++ b/scripts/teacher-imports/assignments/inputs/المعلمات.xlsx
@@ -8,21 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\assignments\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14474A6C-E505-43C3-B82D-56CA6E6D6223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC5D938-84FE-4575-ADCD-E379E85D4B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="3705" windowWidth="22755" windowHeight="7380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2115" yWindow="3750" windowWidth="15705" windowHeight="11655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
     <sheet name="تعليمات" sheetId="2" r:id="rId2"/>
     <sheet name="نسخة من التوزيع" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3114" uniqueCount="448">
   <si>
     <t>بريد المعلم</t>
   </si>
@@ -1072,9 +1083,6 @@
   </si>
   <si>
     <t>mrb-girls-g3-general-1-pe</t>
-  </si>
-  <si>
-    <t>mrb-girls-g3-general-1-life-skills</t>
   </si>
   <si>
     <t>mrb-girls-g3-general-1-art</t>
@@ -1701,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -1748,7 +1756,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B2" t="s">
         <v>289</v>
@@ -1766,7 +1774,7 @@
         <v>317</v>
       </c>
       <c r="G2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2" t="s">
         <v>126</v>
@@ -1776,6 +1784,11 @@
       </c>
       <c r="J2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="B3" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -9168,9 +9181,6 @@
       <c r="F227" t="s">
         <v>65</v>
       </c>
-      <c r="G227" t="s">
-        <v>350</v>
-      </c>
       <c r="H227" t="s">
         <v>56</v>
       </c>
@@ -9201,7 +9211,7 @@
         <v>65</v>
       </c>
       <c r="G228" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H228" t="s">
         <v>38</v>
@@ -9233,7 +9243,7 @@
         <v>84</v>
       </c>
       <c r="G229" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H229" t="s">
         <v>44</v>
@@ -9247,7 +9257,7 @@
     </row>
     <row r="230" spans="1:10">
       <c r="A230" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B230" t="s">
         <v>289</v>
@@ -9265,7 +9275,7 @@
         <v>84</v>
       </c>
       <c r="G230" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H230" t="s">
         <v>145</v>
@@ -9279,7 +9289,7 @@
     </row>
     <row r="231" spans="1:10">
       <c r="A231" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B231" t="s">
         <v>289</v>
@@ -9297,7 +9307,7 @@
         <v>334</v>
       </c>
       <c r="G231" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H231" t="s">
         <v>145</v>
@@ -9311,7 +9321,7 @@
     </row>
     <row r="232" spans="1:10">
       <c r="A232" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B232" t="s">
         <v>289</v>
@@ -9329,7 +9339,7 @@
         <v>334</v>
       </c>
       <c r="G232" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H232" t="s">
         <v>44</v>
@@ -9343,7 +9353,7 @@
     </row>
     <row r="233" spans="1:10">
       <c r="A233" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B233" t="s">
         <v>289</v>
@@ -9361,7 +9371,7 @@
         <v>82</v>
       </c>
       <c r="G233" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H233" t="s">
         <v>145</v>
@@ -9375,7 +9385,7 @@
     </row>
     <row r="234" spans="1:10">
       <c r="A234" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B234" t="s">
         <v>289</v>
@@ -9393,7 +9403,7 @@
         <v>86</v>
       </c>
       <c r="G234" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H234" t="s">
         <v>145</v>
@@ -9407,7 +9417,7 @@
     </row>
     <row r="235" spans="1:10">
       <c r="A235" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B235" t="s">
         <v>289</v>
@@ -9425,7 +9435,7 @@
         <v>308</v>
       </c>
       <c r="G235" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H235" t="s">
         <v>145</v>
@@ -9439,7 +9449,7 @@
     </row>
     <row r="236" spans="1:10">
       <c r="A236" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B236" t="s">
         <v>289</v>
@@ -9457,7 +9467,7 @@
         <v>317</v>
       </c>
       <c r="G236" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H236" t="s">
         <v>145</v>
@@ -9471,7 +9481,7 @@
     </row>
     <row r="237" spans="1:10">
       <c r="A237" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B237" t="s">
         <v>289</v>
@@ -9489,7 +9499,7 @@
         <v>89</v>
       </c>
       <c r="G237" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H237" t="s">
         <v>145</v>
@@ -9503,7 +9513,7 @@
     </row>
     <row r="238" spans="1:10">
       <c r="A238" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B238" t="s">
         <v>289</v>
@@ -9521,7 +9531,7 @@
         <v>89</v>
       </c>
       <c r="G238" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H238" t="s">
         <v>56</v>
@@ -9535,7 +9545,7 @@
     </row>
     <row r="239" spans="1:10">
       <c r="A239" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B239" t="s">
         <v>289</v>
@@ -9547,13 +9557,13 @@
         <v>12</v>
       </c>
       <c r="E239" t="s">
+        <v>363</v>
+      </c>
+      <c r="F239" t="s">
         <v>364</v>
       </c>
-      <c r="F239" t="s">
+      <c r="G239" t="s">
         <v>365</v>
-      </c>
-      <c r="G239" t="s">
-        <v>366</v>
       </c>
       <c r="H239" t="s">
         <v>145</v>
@@ -9567,7 +9577,7 @@
     </row>
     <row r="240" spans="1:10">
       <c r="A240" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B240" t="s">
         <v>289</v>
@@ -9579,13 +9589,13 @@
         <v>12</v>
       </c>
       <c r="E240" t="s">
+        <v>363</v>
+      </c>
+      <c r="F240" t="s">
         <v>364</v>
       </c>
-      <c r="F240" t="s">
-        <v>365</v>
-      </c>
       <c r="G240" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H240" t="s">
         <v>56</v>
@@ -9599,7 +9609,7 @@
     </row>
     <row r="241" spans="1:10">
       <c r="A241" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B241" t="s">
         <v>289</v>
@@ -9617,7 +9627,7 @@
         <v>82</v>
       </c>
       <c r="G241" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H241" t="s">
         <v>105</v>
@@ -9631,7 +9641,7 @@
     </row>
     <row r="242" spans="1:10">
       <c r="A242" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B242" t="s">
         <v>289</v>
@@ -9649,7 +9659,7 @@
         <v>84</v>
       </c>
       <c r="G242" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H242" t="s">
         <v>105</v>
@@ -9663,7 +9673,7 @@
     </row>
     <row r="243" spans="1:10">
       <c r="A243" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B243" t="s">
         <v>289</v>
@@ -9681,7 +9691,7 @@
         <v>84</v>
       </c>
       <c r="G243" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H243" t="s">
         <v>126</v>
@@ -9695,7 +9705,7 @@
     </row>
     <row r="244" spans="1:10">
       <c r="A244" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B244" t="s">
         <v>289</v>
@@ -9713,7 +9723,7 @@
         <v>334</v>
       </c>
       <c r="G244" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H244" t="s">
         <v>105</v>
@@ -9727,7 +9737,7 @@
     </row>
     <row r="245" spans="1:10">
       <c r="A245" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B245" t="s">
         <v>289</v>
@@ -9745,7 +9755,7 @@
         <v>334</v>
       </c>
       <c r="G245" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H245" t="s">
         <v>126</v>
@@ -9759,7 +9769,7 @@
     </row>
     <row r="246" spans="1:10">
       <c r="A246" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B246" t="s">
         <v>289</v>
@@ -9777,7 +9787,7 @@
         <v>86</v>
       </c>
       <c r="G246" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H246" t="s">
         <v>105</v>
@@ -9791,7 +9801,7 @@
     </row>
     <row r="247" spans="1:10">
       <c r="A247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B247" t="s">
         <v>289</v>
@@ -9809,7 +9819,7 @@
         <v>308</v>
       </c>
       <c r="G247" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H247" t="s">
         <v>105</v>
@@ -9823,7 +9833,7 @@
     </row>
     <row r="248" spans="1:10">
       <c r="A248" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B248" t="s">
         <v>289</v>
@@ -9841,7 +9851,7 @@
         <v>308</v>
       </c>
       <c r="G248" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H248" t="s">
         <v>44</v>
@@ -9855,7 +9865,7 @@
     </row>
     <row r="249" spans="1:10">
       <c r="A249" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B249" t="s">
         <v>289</v>
@@ -9873,7 +9883,7 @@
         <v>317</v>
       </c>
       <c r="G249" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H249" t="s">
         <v>105</v>
@@ -9887,7 +9897,7 @@
     </row>
     <row r="250" spans="1:10">
       <c r="A250" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B250" t="s">
         <v>289</v>
@@ -9905,7 +9915,7 @@
         <v>62</v>
       </c>
       <c r="G250" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H250" t="s">
         <v>54</v>
@@ -9919,7 +9929,7 @@
     </row>
     <row r="251" spans="1:10">
       <c r="A251" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B251" t="s">
         <v>289</v>
@@ -9937,7 +9947,7 @@
         <v>52</v>
       </c>
       <c r="G251" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H251" t="s">
         <v>54</v>
@@ -9951,7 +9961,7 @@
     </row>
     <row r="252" spans="1:10">
       <c r="A252" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B252" t="s">
         <v>289</v>
@@ -9969,7 +9979,7 @@
         <v>69</v>
       </c>
       <c r="G252" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H252" t="s">
         <v>54</v>
@@ -9983,7 +9993,7 @@
     </row>
     <row r="253" spans="1:10">
       <c r="A253" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B253" t="s">
         <v>289</v>
@@ -10001,7 +10011,7 @@
         <v>72</v>
       </c>
       <c r="G253" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H253" t="s">
         <v>54</v>
@@ -10015,7 +10025,7 @@
     </row>
     <row r="254" spans="1:10">
       <c r="A254" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B254" t="s">
         <v>289</v>
@@ -10033,7 +10043,7 @@
         <v>82</v>
       </c>
       <c r="G254" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H254" t="s">
         <v>44</v>
@@ -10047,7 +10057,7 @@
     </row>
     <row r="255" spans="1:10">
       <c r="A255" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B255" t="s">
         <v>289</v>
@@ -10065,7 +10075,7 @@
         <v>75</v>
       </c>
       <c r="G255" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H255" t="s">
         <v>54</v>
@@ -10079,7 +10089,7 @@
     </row>
     <row r="256" spans="1:10">
       <c r="A256" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B256" t="s">
         <v>289</v>
@@ -10097,7 +10107,7 @@
         <v>65</v>
       </c>
       <c r="G256" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H256" t="s">
         <v>54</v>
@@ -10111,7 +10121,7 @@
     </row>
     <row r="257" spans="1:10">
       <c r="A257" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B257" t="s">
         <v>289</v>
@@ -10129,7 +10139,7 @@
         <v>78</v>
       </c>
       <c r="G257" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H257" t="s">
         <v>54</v>
@@ -10143,7 +10153,7 @@
     </row>
     <row r="258" spans="1:10">
       <c r="A258" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B258" t="s">
         <v>289</v>
@@ -10161,7 +10171,7 @@
         <v>338</v>
       </c>
       <c r="G258" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H258" t="s">
         <v>54</v>
@@ -10175,7 +10185,7 @@
     </row>
     <row r="259" spans="1:10">
       <c r="A259" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B259" t="s">
         <v>289</v>
@@ -10187,13 +10197,13 @@
         <v>12</v>
       </c>
       <c r="E259" t="s">
+        <v>363</v>
+      </c>
+      <c r="F259" t="s">
         <v>364</v>
       </c>
-      <c r="F259" t="s">
-        <v>365</v>
-      </c>
       <c r="G259" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H259" t="s">
         <v>44</v>
@@ -10207,7 +10217,7 @@
     </row>
     <row r="260" spans="1:10">
       <c r="A260" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B260" t="s">
         <v>289</v>
@@ -10225,7 +10235,7 @@
         <v>84</v>
       </c>
       <c r="G260" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H260" t="s">
         <v>54</v>
@@ -10239,7 +10249,7 @@
     </row>
     <row r="261" spans="1:10">
       <c r="A261" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B261" t="s">
         <v>289</v>
@@ -10257,7 +10267,7 @@
         <v>334</v>
       </c>
       <c r="G261" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H261" t="s">
         <v>54</v>
@@ -10271,7 +10281,7 @@
     </row>
     <row r="262" spans="1:10">
       <c r="A262" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B262" t="s">
         <v>289</v>
@@ -10289,7 +10299,7 @@
         <v>82</v>
       </c>
       <c r="G262" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H262" t="s">
         <v>54</v>
@@ -10303,7 +10313,7 @@
     </row>
     <row r="263" spans="1:10">
       <c r="A263" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B263" t="s">
         <v>289</v>
@@ -10321,7 +10331,7 @@
         <v>86</v>
       </c>
       <c r="G263" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H263" t="s">
         <v>54</v>
@@ -10335,7 +10345,7 @@
     </row>
     <row r="264" spans="1:10">
       <c r="A264" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B264" t="s">
         <v>289</v>
@@ -10353,7 +10363,7 @@
         <v>86</v>
       </c>
       <c r="G264" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H264" t="s">
         <v>44</v>
@@ -10367,7 +10377,7 @@
     </row>
     <row r="265" spans="1:10">
       <c r="A265" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B265" t="s">
         <v>289</v>
@@ -10385,7 +10395,7 @@
         <v>308</v>
       </c>
       <c r="G265" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H265" t="s">
         <v>54</v>
@@ -10399,7 +10409,7 @@
     </row>
     <row r="266" spans="1:10">
       <c r="A266" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B266" t="s">
         <v>289</v>
@@ -10417,7 +10427,7 @@
         <v>317</v>
       </c>
       <c r="G266" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H266" t="s">
         <v>54</v>
@@ -10431,7 +10441,7 @@
     </row>
     <row r="267" spans="1:10">
       <c r="A267" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B267" t="s">
         <v>289</v>
@@ -10449,7 +10459,7 @@
         <v>317</v>
       </c>
       <c r="G267" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H267" t="s">
         <v>44</v>
@@ -10463,7 +10473,7 @@
     </row>
     <row r="268" spans="1:10">
       <c r="A268" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B268" t="s">
         <v>289</v>
@@ -10481,7 +10491,7 @@
         <v>89</v>
       </c>
       <c r="G268" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H268" t="s">
         <v>54</v>
@@ -10495,7 +10505,7 @@
     </row>
     <row r="269" spans="1:10">
       <c r="A269" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B269" t="s">
         <v>289</v>
@@ -10507,13 +10517,13 @@
         <v>12</v>
       </c>
       <c r="E269" t="s">
+        <v>363</v>
+      </c>
+      <c r="F269" t="s">
         <v>364</v>
       </c>
-      <c r="F269" t="s">
-        <v>365</v>
-      </c>
       <c r="G269" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H269" t="s">
         <v>54</v>
@@ -10527,7 +10537,7 @@
     </row>
     <row r="270" spans="1:10">
       <c r="A270" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B270" t="s">
         <v>289</v>
@@ -10545,7 +10555,7 @@
         <v>52</v>
       </c>
       <c r="G270" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H270" t="s">
         <v>31</v>
@@ -10559,7 +10569,7 @@
     </row>
     <row r="271" spans="1:10">
       <c r="A271" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B271" t="s">
         <v>289</v>
@@ -10577,7 +10587,7 @@
         <v>62</v>
       </c>
       <c r="G271" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H271" t="s">
         <v>31</v>
@@ -10591,7 +10601,7 @@
     </row>
     <row r="272" spans="1:10">
       <c r="A272" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B272" t="s">
         <v>289</v>
@@ -10609,7 +10619,7 @@
         <v>69</v>
       </c>
       <c r="G272" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H272" t="s">
         <v>31</v>
@@ -10623,7 +10633,7 @@
     </row>
     <row r="273" spans="1:10">
       <c r="A273" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B273" t="s">
         <v>289</v>
@@ -10641,7 +10651,7 @@
         <v>72</v>
       </c>
       <c r="G273" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H273" t="s">
         <v>31</v>
@@ -10655,7 +10665,7 @@
     </row>
     <row r="274" spans="1:10">
       <c r="A274" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B274" t="s">
         <v>289</v>
@@ -10673,7 +10683,7 @@
         <v>75</v>
       </c>
       <c r="G274" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H274" t="s">
         <v>31</v>
@@ -10687,7 +10697,7 @@
     </row>
     <row r="275" spans="1:10">
       <c r="A275" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B275" t="s">
         <v>289</v>
@@ -10705,7 +10715,7 @@
         <v>82</v>
       </c>
       <c r="G275" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H275" t="s">
         <v>31</v>
@@ -10719,7 +10729,7 @@
     </row>
     <row r="276" spans="1:10">
       <c r="A276" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B276" t="s">
         <v>289</v>
@@ -10737,7 +10747,7 @@
         <v>82</v>
       </c>
       <c r="G276" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H276" t="s">
         <v>112</v>
@@ -10751,7 +10761,7 @@
     </row>
     <row r="277" spans="1:10">
       <c r="A277" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B277" t="s">
         <v>289</v>
@@ -10769,7 +10779,7 @@
         <v>82</v>
       </c>
       <c r="G277" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H277" t="s">
         <v>38</v>
@@ -10783,7 +10793,7 @@
     </row>
     <row r="278" spans="1:10">
       <c r="A278" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B278" t="s">
         <v>289</v>
@@ -10801,7 +10811,7 @@
         <v>84</v>
       </c>
       <c r="G278" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H278" t="s">
         <v>31</v>
@@ -10815,7 +10825,7 @@
     </row>
     <row r="279" spans="1:10">
       <c r="A279" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B279" t="s">
         <v>289</v>
@@ -10833,7 +10843,7 @@
         <v>84</v>
       </c>
       <c r="G279" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H279" t="s">
         <v>112</v>
@@ -10847,7 +10857,7 @@
     </row>
     <row r="280" spans="1:10">
       <c r="A280" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B280" t="s">
         <v>289</v>
@@ -10865,7 +10875,7 @@
         <v>334</v>
       </c>
       <c r="G280" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H280" t="s">
         <v>31</v>
@@ -10879,7 +10889,7 @@
     </row>
     <row r="281" spans="1:10">
       <c r="A281" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B281" t="s">
         <v>289</v>
@@ -10897,7 +10907,7 @@
         <v>334</v>
       </c>
       <c r="G281" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H281" t="s">
         <v>112</v>
@@ -10911,7 +10921,7 @@
     </row>
     <row r="282" spans="1:10">
       <c r="A282" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B282" t="s">
         <v>289</v>
@@ -10929,7 +10939,7 @@
         <v>308</v>
       </c>
       <c r="G282" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H282" t="s">
         <v>31</v>
@@ -10943,7 +10953,7 @@
     </row>
     <row r="283" spans="1:10">
       <c r="A283" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B283" t="s">
         <v>289</v>
@@ -10961,7 +10971,7 @@
         <v>317</v>
       </c>
       <c r="G283" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H283" t="s">
         <v>31</v>
@@ -10975,7 +10985,7 @@
     </row>
     <row r="284" spans="1:10">
       <c r="A284" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B284" t="s">
         <v>289</v>
@@ -10993,7 +11003,7 @@
         <v>89</v>
       </c>
       <c r="G284" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H284" t="s">
         <v>31</v>
@@ -11007,7 +11017,7 @@
     </row>
     <row r="285" spans="1:10">
       <c r="A285" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B285" t="s">
         <v>289</v>
@@ -11025,7 +11035,7 @@
         <v>89</v>
       </c>
       <c r="G285" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H285" t="s">
         <v>38</v>
@@ -11039,7 +11049,7 @@
     </row>
     <row r="286" spans="1:10">
       <c r="A286" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B286" t="s">
         <v>289</v>
@@ -11051,13 +11061,13 @@
         <v>12</v>
       </c>
       <c r="E286" t="s">
+        <v>363</v>
+      </c>
+      <c r="F286" t="s">
         <v>364</v>
       </c>
-      <c r="F286" t="s">
-        <v>365</v>
-      </c>
       <c r="G286" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H286" t="s">
         <v>31</v>
@@ -11071,7 +11081,7 @@
     </row>
     <row r="287" spans="1:10">
       <c r="A287" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B287" t="s">
         <v>289</v>
@@ -11083,13 +11093,13 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
+        <v>363</v>
+      </c>
+      <c r="F287" t="s">
         <v>364</v>
       </c>
-      <c r="F287" t="s">
-        <v>365</v>
-      </c>
       <c r="G287" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H287" t="s">
         <v>38</v>
@@ -11103,7 +11113,7 @@
     </row>
     <row r="288" spans="1:10">
       <c r="A288" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B288" t="s">
         <v>289</v>
@@ -11121,7 +11131,7 @@
         <v>65</v>
       </c>
       <c r="G288" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H288" t="s">
         <v>31</v>
@@ -11135,7 +11145,7 @@
     </row>
     <row r="289" spans="1:10">
       <c r="A289" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B289" t="s">
         <v>289</v>
@@ -11153,7 +11163,7 @@
         <v>78</v>
       </c>
       <c r="G289" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H289" t="s">
         <v>31</v>
@@ -11167,7 +11177,7 @@
     </row>
     <row r="290" spans="1:10">
       <c r="A290" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B290" t="s">
         <v>289</v>
@@ -11185,7 +11195,7 @@
         <v>338</v>
       </c>
       <c r="G290" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H290" t="s">
         <v>31</v>
@@ -11199,7 +11209,7 @@
     </row>
     <row r="291" spans="1:10">
       <c r="A291" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B291" t="s">
         <v>289</v>
@@ -11217,7 +11227,7 @@
         <v>86</v>
       </c>
       <c r="G291" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H291" t="s">
         <v>31</v>
@@ -11231,7 +11241,7 @@
     </row>
     <row r="292" spans="1:10">
       <c r="A292" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B292" t="s">
         <v>289</v>
@@ -11249,7 +11259,7 @@
         <v>52</v>
       </c>
       <c r="G292" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H292" t="s">
         <v>179</v>
@@ -11263,7 +11273,7 @@
     </row>
     <row r="293" spans="1:10">
       <c r="A293" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B293" t="s">
         <v>289</v>
@@ -11281,7 +11291,7 @@
         <v>62</v>
       </c>
       <c r="G293" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H293" t="s">
         <v>179</v>
@@ -11295,7 +11305,7 @@
     </row>
     <row r="294" spans="1:10">
       <c r="A294" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B294" t="s">
         <v>289</v>
@@ -11313,7 +11323,7 @@
         <v>69</v>
       </c>
       <c r="G294" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H294" t="s">
         <v>179</v>
@@ -11327,7 +11337,7 @@
     </row>
     <row r="295" spans="1:10">
       <c r="A295" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B295" t="s">
         <v>289</v>
@@ -11345,7 +11355,7 @@
         <v>72</v>
       </c>
       <c r="G295" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H295" t="s">
         <v>179</v>
@@ -11359,7 +11369,7 @@
     </row>
     <row r="296" spans="1:10">
       <c r="A296" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B296" t="s">
         <v>289</v>
@@ -11377,7 +11387,7 @@
         <v>75</v>
       </c>
       <c r="G296" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H296" t="s">
         <v>179</v>
@@ -11391,7 +11401,7 @@
     </row>
     <row r="297" spans="1:10">
       <c r="A297" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B297" t="s">
         <v>289</v>
@@ -11409,7 +11419,7 @@
         <v>86</v>
       </c>
       <c r="G297" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H297" t="s">
         <v>112</v>
@@ -11423,7 +11433,7 @@
     </row>
     <row r="298" spans="1:10">
       <c r="A298" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B298" t="s">
         <v>289</v>
@@ -11441,7 +11451,7 @@
         <v>86</v>
       </c>
       <c r="G298" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H298" t="s">
         <v>56</v>
@@ -11455,7 +11465,7 @@
     </row>
     <row r="299" spans="1:10">
       <c r="A299" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B299" t="s">
         <v>289</v>
@@ -11473,7 +11483,7 @@
         <v>308</v>
       </c>
       <c r="G299" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H299" t="s">
         <v>112</v>
@@ -11487,7 +11497,7 @@
     </row>
     <row r="300" spans="1:10">
       <c r="A300" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B300" t="s">
         <v>289</v>
@@ -11505,7 +11515,7 @@
         <v>317</v>
       </c>
       <c r="G300" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H300" t="s">
         <v>112</v>
@@ -11519,7 +11529,7 @@
     </row>
     <row r="301" spans="1:10">
       <c r="A301" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B301" t="s">
         <v>289</v>
@@ -11537,7 +11547,7 @@
         <v>86</v>
       </c>
       <c r="G301" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H301" t="s">
         <v>179</v>
@@ -11551,7 +11561,7 @@
     </row>
     <row r="302" spans="1:10">
       <c r="A302" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B302" t="s">
         <v>289</v>
@@ -11569,7 +11579,7 @@
         <v>308</v>
       </c>
       <c r="G302" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H302" t="s">
         <v>179</v>
@@ -11583,7 +11593,7 @@
     </row>
     <row r="303" spans="1:10">
       <c r="A303" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B303" t="s">
         <v>289</v>
@@ -11601,7 +11611,7 @@
         <v>308</v>
       </c>
       <c r="G303" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H303" t="s">
         <v>56</v>
@@ -11615,7 +11625,7 @@
     </row>
     <row r="304" spans="1:10">
       <c r="A304" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B304" t="s">
         <v>289</v>
@@ -11633,7 +11643,7 @@
         <v>317</v>
       </c>
       <c r="G304" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H304" t="s">
         <v>179</v>
@@ -11647,7 +11657,7 @@
     </row>
     <row r="305" spans="1:10">
       <c r="A305" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B305" t="s">
         <v>289</v>
@@ -11665,7 +11675,7 @@
         <v>317</v>
       </c>
       <c r="G305" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H305" t="s">
         <v>56</v>
@@ -11679,7 +11689,7 @@
     </row>
     <row r="306" spans="1:10">
       <c r="A306" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B306" t="s">
         <v>289</v>
@@ -11697,7 +11707,7 @@
         <v>89</v>
       </c>
       <c r="G306" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H306" t="s">
         <v>179</v>
@@ -11711,7 +11721,7 @@
     </row>
     <row r="307" spans="1:10">
       <c r="A307" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B307" t="s">
         <v>289</v>
@@ -11723,13 +11733,13 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
+        <v>363</v>
+      </c>
+      <c r="F307" t="s">
         <v>364</v>
       </c>
-      <c r="F307" t="s">
-        <v>365</v>
-      </c>
       <c r="G307" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H307" t="s">
         <v>179</v>
